--- a/IT23192096-Test Cases.xlsx
+++ b/IT23192096-Test Cases.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39416620-FD93-4A06-A234-C9317A1BF4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name=" Test cases" sheetId="1" r:id="rId1"/>
